--- a/databaza_pozicii.xlsx
+++ b/databaza_pozicii.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16485" windowHeight="12420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1564" uniqueCount="129">
   <si>
     <t>Priezvisko</t>
   </si>
@@ -399,180 +399,6 @@
   </si>
   <si>
     <t>Volno</t>
-  </si>
-  <si>
-    <t>17-21</t>
-  </si>
-  <si>
-    <t>14-16,22-24</t>
-  </si>
-  <si>
-    <t>20-24</t>
-  </si>
-  <si>
-    <t>18-20</t>
-  </si>
-  <si>
-    <t>19,22-24</t>
-  </si>
-  <si>
-    <t>3,4,6-8,14</t>
-  </si>
-  <si>
-    <t>12,20,25</t>
-  </si>
-  <si>
-    <t>14-15</t>
-  </si>
-  <si>
-    <t>6,7,10,11</t>
-  </si>
-  <si>
-    <t>24-30</t>
-  </si>
-  <si>
-    <t>12-31</t>
-  </si>
-  <si>
-    <t>8-10</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>30-31</t>
-  </si>
-  <si>
-    <t>3,9-11,19,24-27</t>
-  </si>
-  <si>
-    <t>28-30</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>9-13</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>26,31</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>9,20-22</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20-22</t>
-  </si>
-  <si>
-    <t>17-23</t>
-  </si>
-  <si>
-    <t>2,13,14</t>
-  </si>
-  <si>
-    <t>13-22</t>
-  </si>
-  <si>
-    <t>6,8,10</t>
-  </si>
-  <si>
-    <t>4-6,12-14,20-22,26,28-30</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2,23</t>
-  </si>
-  <si>
-    <t>26-31</t>
-  </si>
-  <si>
-    <t>1-8</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>17-20</t>
-  </si>
-  <si>
-    <t>14-21</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>2-12</t>
-  </si>
-  <si>
-    <t>20-21</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>8-11</t>
-  </si>
-  <si>
-    <t>27-29</t>
-  </si>
-  <si>
-    <t>18-24,28-31</t>
-  </si>
-  <si>
-    <t>17-27</t>
-  </si>
-  <si>
-    <t>5-6</t>
-  </si>
-  <si>
-    <t>21-23</t>
   </si>
   <si>
     <t>Velitel</t>
@@ -1005,7 +831,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -1017,7 +843,7 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>8</v>
@@ -1035,13 +861,13 @@
         <v>12</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>14</v>
@@ -1820,10 +1646,10 @@
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -3815,7 +3641,7 @@
         <v>77</v>
       </c>
       <c r="B35" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -6020,15 +5846,6 @@
         <f>Data!B2</f>
         <v>František</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="D2" s="2">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="str">
@@ -6039,12 +5856,6 @@
         <f>Data!B3</f>
         <v>Alojz</v>
       </c>
-      <c r="D3" s="2">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2">
-        <v>10</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
@@ -6055,9 +5866,6 @@
         <f>Data!B4</f>
         <v>Martin</v>
       </c>
-      <c r="E4" s="2">
-        <v>19</v>
-      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
@@ -6068,9 +5876,6 @@
         <f>Data!B5</f>
         <v>Martin</v>
       </c>
-      <c r="D5" s="2">
-        <v>17</v>
-      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="str">
@@ -6081,9 +5886,6 @@
         <f>Data!B6</f>
         <v>Miroslav</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="str">
@@ -6094,12 +5896,6 @@
         <f>Data!B7</f>
         <v>Arpád</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="D7" s="2">
-        <v>17</v>
-      </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="str">
@@ -6110,15 +5906,6 @@
         <f>Data!B8</f>
         <v>Ľubomír</v>
       </c>
-      <c r="C8" s="2">
-        <v>20</v>
-      </c>
-      <c r="D8" s="2">
-        <v>21</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="str">
@@ -6129,15 +5916,6 @@
         <f>Data!B9</f>
         <v>Ján</v>
       </c>
-      <c r="C9" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="D9" s="2">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="str">
@@ -6148,12 +5926,6 @@
         <f>Data!B10</f>
         <v>Ondrej</v>
       </c>
-      <c r="C10" s="2">
-        <v>5</v>
-      </c>
-      <c r="D10" s="2">
-        <v>4</v>
-      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="str">
@@ -6164,12 +5936,6 @@
         <f>Data!B11</f>
         <v>Mario</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="2">
-        <v>9</v>
-      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="str">
@@ -6180,12 +5946,6 @@
         <f>Data!B12</f>
         <v>Andrej</v>
       </c>
-      <c r="C12" s="2">
-        <v>13</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>129</v>
-      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="str">
@@ -6196,15 +5956,6 @@
         <f>Data!B13</f>
         <v>Peter</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="D13" s="2">
-        <v>26</v>
-      </c>
-      <c r="E13" s="2">
-        <v>27</v>
-      </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="str">
@@ -6215,9 +5966,6 @@
         <f>Data!B14</f>
         <v>Stanislav</v>
       </c>
-      <c r="C14" s="2">
-        <v>14</v>
-      </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="str">
@@ -6228,12 +5976,6 @@
         <f>Data!B15</f>
         <v>Michal</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D15" s="2">
-        <v>31</v>
-      </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="str">
@@ -6245,7 +5987,7 @@
         <v>Richard</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="str">
         <f>Data!A17</f>
         <v>Panca</v>
@@ -6254,17 +5996,8 @@
         <f>Data!B17</f>
         <v>Roman</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="2">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="str">
         <f>Data!A18</f>
         <v>Kleinedler</v>
@@ -6273,14 +6006,8 @@
         <f>Data!B18</f>
         <v>Vladimír</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="str">
         <f>Data!A19</f>
         <v>Zmeko</v>
@@ -6289,11 +6016,8 @@
         <f>Data!B19</f>
         <v>Milan</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="str">
         <f>Data!A20</f>
         <v>Rigo</v>
@@ -6302,11 +6026,8 @@
         <f>Data!B20</f>
         <v>Otto</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f>Data!A21</f>
         <v>Klempa</v>
@@ -6315,17 +6036,8 @@
         <f>Data!B21</f>
         <v>Juraj</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f>Data!A22</f>
         <v>Mračna</v>
@@ -6334,17 +6046,8 @@
         <f>Data!B22</f>
         <v>Vladimír</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f>Data!A23</f>
         <v>Bila</v>
@@ -6353,14 +6056,8 @@
         <f>Data!B23</f>
         <v>Roland</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="str">
         <f>Data!A25</f>
         <v>Mikloško</v>
@@ -6370,7 +6067,7 @@
         <v>Miloš</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f>Data!A26</f>
         <v>Cabadaj</v>
@@ -6379,11 +6076,8 @@
         <f>Data!B26</f>
         <v>Jozef</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="str">
         <f>Data!A27</f>
         <v>Tomka</v>
@@ -6392,11 +6086,8 @@
         <f>Data!B27</f>
         <v>Jozef</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f>Data!A28</f>
         <v>Zezula</v>
@@ -6405,17 +6096,8 @@
         <f>Data!B28</f>
         <v>Viliam</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="str">
         <f>Data!A29</f>
         <v>Palič</v>
@@ -6424,11 +6106,8 @@
         <f>Data!B29</f>
         <v>Karol</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="str">
         <f>Data!A30</f>
         <v>Kováč</v>
@@ -6437,11 +6116,8 @@
         <f>Data!B30</f>
         <v>Tibor</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="str">
         <f>Data!A31</f>
         <v>Petriska</v>
@@ -6450,14 +6126,8 @@
         <f>Data!B31</f>
         <v>Branislav</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="str">
         <f>Data!A32</f>
         <v>Duba</v>
@@ -6466,14 +6136,8 @@
         <f>Data!B32</f>
         <v>Peter</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="str">
         <f>Data!A33</f>
         <v>Žolnay</v>
@@ -6482,14 +6146,8 @@
         <f>Data!B33</f>
         <v>Martin</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f>Data!A34</f>
         <v>Vydra</v>
@@ -6498,11 +6156,8 @@
         <f>Data!B34</f>
         <v>Richard</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="str">
         <f>Data!A36</f>
         <v>Urmín</v>
@@ -6511,11 +6166,8 @@
         <f>Data!B36</f>
         <v>Roman</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f>Data!A37</f>
         <v>Veselý</v>
@@ -6524,17 +6176,8 @@
         <f>Data!B37</f>
         <v>Jaroslav</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="str">
         <f>Data!A38</f>
         <v>Tóth</v>
@@ -6543,11 +6186,8 @@
         <f>Data!B38</f>
         <v>Mikuláš</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="str">
         <f>Data!A39</f>
         <v>Valachovič</v>
@@ -6556,11 +6196,8 @@
         <f>Data!B39</f>
         <v>Martin</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="str">
         <f>Data!A40</f>
         <v>Kotrla</v>
@@ -6569,14 +6206,8 @@
         <f>Data!B40</f>
         <v>Anton</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="str">
         <f>Data!A41</f>
         <v>Sojka</v>
@@ -6585,14 +6216,8 @@
         <f>Data!B41</f>
         <v>Štefan</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="str">
         <f>Data!A42</f>
         <v>Kalafút</v>
@@ -6601,14 +6226,8 @@
         <f>Data!B42</f>
         <v>Daniel</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="str">
         <f>Data!A43</f>
         <v>Srnec</v>
@@ -6618,7 +6237,7 @@
         <v>Radovan</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="str">
         <f>Data!A44</f>
         <v>Puhovich</v>
@@ -6627,17 +6246,8 @@
         <f>Data!B44</f>
         <v>Iveta</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="str">
         <f>Data!A45</f>
         <v>Hrubý</v>
@@ -6646,11 +6256,8 @@
         <f>Data!B45</f>
         <v>Erik</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="str">
         <f>Data!A46</f>
         <v>Molnár</v>
@@ -6660,7 +6267,7 @@
         <v>Miroslav</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="str">
         <f>Data!A47</f>
         <v>Haluska</v>
@@ -6669,11 +6276,8 @@
         <f>Data!B47</f>
         <v>Martin</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="str">
         <f>Data!A48</f>
         <v>Mateovič</v>
@@ -6682,11 +6286,8 @@
         <f>Data!B48</f>
         <v>Ondrej</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="str">
         <f>Data!A49</f>
         <v>Hitmar</v>
@@ -6696,7 +6297,7 @@
         <v>Peter</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="str">
         <f>Data!A50</f>
         <v>Fojta</v>
@@ -6705,14 +6306,8 @@
         <f>Data!B50</f>
         <v>Ondrej</v>
       </c>
-      <c r="D48" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="str">
         <f>Data!A51</f>
         <v>Lazovská</v>
@@ -6721,11 +6316,8 @@
         <f>Data!B51</f>
         <v>Sylvia</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="str">
         <f>Data!A52</f>
         <v>Fojta</v>
@@ -6734,17 +6326,8 @@
         <f>Data!B52</f>
         <v>Peter</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="str">
         <f>Data!A53</f>
         <v>Krampl</v>
@@ -6753,11 +6336,8 @@
         <f>Data!B53</f>
         <v>Róbert</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="str">
         <f>Data!A54</f>
         <v>Tóth</v>
@@ -6766,14 +6346,8 @@
         <f>Data!B54</f>
         <v>Marian</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="str">
         <f>Data!A55</f>
         <v>Roško</v>
@@ -6783,7 +6357,7 @@
         <v>Martin</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="str">
         <f>Data!A56</f>
         <v>Fojta</v>
@@ -6793,7 +6367,7 @@
         <v>Jozef</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="str">
         <f>Data!A57</f>
         <v>Onduško</v>
@@ -6802,14 +6376,8 @@
         <f>Data!B57</f>
         <v>Ján</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="str">
         <f>Data!A58</f>
         <v>Šoltésová</v>
@@ -6818,11 +6386,8 @@
         <f>Data!B58</f>
         <v>Veronika</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="str">
         <f>Data!A59</f>
         <v>Tvrdá</v>
@@ -6832,7 +6397,7 @@
         <v>Rebeka</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="str">
         <f>Data!A60</f>
         <v>Ferčáková</v>
@@ -6840,9 +6405,6 @@
       <c r="B58" t="str">
         <f>Data!B60</f>
         <v>Monika</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>
